--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/102.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/102.xlsx
@@ -426,13 +426,13 @@
         <v>-24.94283276758118</v>
       </c>
       <c r="E2">
-        <v>-26.49266905559819</v>
+        <v>-16.47465818044337</v>
       </c>
       <c r="F2">
-        <v>-5.629139355010242</v>
+        <v>-2.742634325869766</v>
       </c>
       <c r="G2">
-        <v>-17.84599996135571</v>
+        <v>-13.22672340172747</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-24.56065419997829</v>
       </c>
       <c r="E3">
-        <v>-27.97325982042029</v>
+        <v>-16.76608901910659</v>
       </c>
       <c r="F3">
-        <v>-5.533047079550694</v>
+        <v>-2.577602001679631</v>
       </c>
       <c r="G3">
-        <v>-16.30314389481304</v>
+        <v>-13.14111708658486</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-24.11457284211897</v>
       </c>
       <c r="E4">
-        <v>-27.97056438627048</v>
+        <v>-16.97957654083675</v>
       </c>
       <c r="F4">
-        <v>-5.572526241600715</v>
+        <v>-2.625556190627695</v>
       </c>
       <c r="G4">
-        <v>-15.96863310647058</v>
+        <v>-12.65615169820114</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-23.65383548222551</v>
       </c>
       <c r="E5">
-        <v>-28.46142204972365</v>
+        <v>-17.64029847086975</v>
       </c>
       <c r="F5">
-        <v>-5.272242229718492</v>
+        <v>-2.852638203491929</v>
       </c>
       <c r="G5">
-        <v>-16.17969614219454</v>
+        <v>-12.58538877143131</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-23.16883068501365</v>
       </c>
       <c r="E6">
-        <v>-30.62116046662135</v>
+        <v>-17.94957981180708</v>
       </c>
       <c r="F6">
-        <v>-5.139027497469886</v>
+        <v>-2.768885288864482</v>
       </c>
       <c r="G6">
-        <v>-15.99623389828783</v>
+        <v>-12.31807593811951</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-22.67633859982959</v>
       </c>
       <c r="E7">
-        <v>-28.20654777714157</v>
+        <v>-19.05800546302262</v>
       </c>
       <c r="F7">
-        <v>-5.008475138053878</v>
+        <v>-2.422119925276373</v>
       </c>
       <c r="G7">
-        <v>-15.71892452393666</v>
+        <v>-11.55441356463444</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-22.17520520045574</v>
       </c>
       <c r="E8">
-        <v>-29.38655194893487</v>
+        <v>-20.04771572172926</v>
       </c>
       <c r="F8">
-        <v>-5.442659770394226</v>
+        <v>-2.322256921399281</v>
       </c>
       <c r="G8">
-        <v>-15.62447170074707</v>
+        <v>-10.98134076778983</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-21.6766026109012</v>
       </c>
       <c r="E9">
-        <v>-28.91667007927775</v>
+        <v>-20.13843846990882</v>
       </c>
       <c r="F9">
-        <v>-4.446414601375969</v>
+        <v>-2.463721364612367</v>
       </c>
       <c r="G9">
-        <v>-15.93558369069168</v>
+        <v>-10.20474476560038</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-21.19056396391309</v>
       </c>
       <c r="E10">
-        <v>-29.57094830194027</v>
+        <v>-21.11760787827304</v>
       </c>
       <c r="F10">
-        <v>-5.208046241103738</v>
+        <v>-1.988308058267285</v>
       </c>
       <c r="G10">
-        <v>-15.15988447926928</v>
+        <v>-10.60863609145168</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-20.7265388085075</v>
       </c>
       <c r="E11">
-        <v>-30.40750473983254</v>
+        <v>-21.73932700075457</v>
       </c>
       <c r="F11">
-        <v>-5.090603624204435</v>
+        <v>-2.093143751663383</v>
       </c>
       <c r="G11">
-        <v>-14.68280484492301</v>
+        <v>-9.639175248710623</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-20.30874881322586</v>
       </c>
       <c r="E12">
-        <v>-29.90825966610887</v>
+        <v>-22.2135406698235</v>
       </c>
       <c r="F12">
-        <v>-5.485275131431246</v>
+        <v>-1.654522383513642</v>
       </c>
       <c r="G12">
-        <v>-14.75852296492677</v>
+        <v>-9.0196873291529</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-19.93876016973021</v>
       </c>
       <c r="E13">
-        <v>-30.8158858561916</v>
+        <v>-22.54676527404847</v>
       </c>
       <c r="F13">
-        <v>-5.139926276101924</v>
+        <v>-1.898653854262295</v>
       </c>
       <c r="G13">
-        <v>-13.66774082103669</v>
+        <v>-8.821054048427227</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-19.63280671003669</v>
       </c>
       <c r="E14">
-        <v>-32.32155994081</v>
+        <v>-24.28716432650654</v>
       </c>
       <c r="F14">
-        <v>-4.890349118047267</v>
+        <v>-1.421098389813575</v>
       </c>
       <c r="G14">
-        <v>-14.67920332275957</v>
+        <v>-8.440744273095163</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-19.37273452076528</v>
       </c>
       <c r="E15">
-        <v>-34.23308375948499</v>
+        <v>-24.45344229510738</v>
       </c>
       <c r="F15">
-        <v>-4.27531200085812</v>
+        <v>-1.219123364560791</v>
       </c>
       <c r="G15">
-        <v>-14.09762472003711</v>
+        <v>-8.594410088983501</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-19.15002162493973</v>
       </c>
       <c r="E16">
-        <v>-33.75697830265761</v>
+        <v>-25.69487453900055</v>
       </c>
       <c r="F16">
-        <v>-4.192022143608838</v>
+        <v>-0.8398536924542314</v>
       </c>
       <c r="G16">
-        <v>-13.54122413815134</v>
+        <v>-7.796083554189924</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-18.93786827893273</v>
       </c>
       <c r="E17">
-        <v>-34.34351349540086</v>
+        <v>-26.46921171803556</v>
       </c>
       <c r="F17">
-        <v>-4.400436068683582</v>
+        <v>-1.169480134478419</v>
       </c>
       <c r="G17">
-        <v>-13.99522609568446</v>
+        <v>-7.958616764081977</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-18.72647364074585</v>
       </c>
       <c r="E18">
-        <v>-34.94393079699734</v>
+        <v>-26.25187001619596</v>
       </c>
       <c r="F18">
-        <v>-4.526374421665997</v>
+        <v>-0.7488691304003449</v>
       </c>
       <c r="G18">
-        <v>-12.96035043646848</v>
+        <v>-7.858559977627561</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-18.50164746476468</v>
       </c>
       <c r="E19">
-        <v>-35.45250190675091</v>
+        <v>-27.85612680142615</v>
       </c>
       <c r="F19">
-        <v>-4.598652791029865</v>
+        <v>-0.4873295186818597</v>
       </c>
       <c r="G19">
-        <v>-12.47400265882376</v>
+        <v>-7.695790495350012</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-18.26352287612533</v>
       </c>
       <c r="E20">
-        <v>-35.40413983747894</v>
+        <v>-28.6870597911846</v>
       </c>
       <c r="F20">
-        <v>-3.955697207264167</v>
+        <v>-0.1271371478617731</v>
       </c>
       <c r="G20">
-        <v>-12.98283416888714</v>
+        <v>-7.483381620789331</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-18.00464622418916</v>
       </c>
       <c r="E21">
-        <v>-36.50785574705213</v>
+        <v>-28.9589996091004</v>
       </c>
       <c r="F21">
-        <v>-3.003468996928468</v>
+        <v>-0.05232728771494972</v>
       </c>
       <c r="G21">
-        <v>-11.96717750597864</v>
+        <v>-7.337250413790946</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-17.72572529901941</v>
       </c>
       <c r="E22">
-        <v>-36.2127513929721</v>
+        <v>-28.86901197932534</v>
       </c>
       <c r="F22">
-        <v>-3.293072039518995</v>
+        <v>0.3560015128818162</v>
       </c>
       <c r="G22">
-        <v>-12.79080085048781</v>
+        <v>-7.66106628691591</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-17.42376757940783</v>
       </c>
       <c r="E23">
-        <v>-37.96509715780605</v>
+        <v>-29.23479153051997</v>
       </c>
       <c r="F23">
-        <v>-3.672137104877063</v>
+        <v>0.5122639113785121</v>
       </c>
       <c r="G23">
-        <v>-12.95745773146152</v>
+        <v>-7.534022233623155</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-17.10319921761738</v>
       </c>
       <c r="E24">
-        <v>-37.55965236185364</v>
+        <v>-29.33418826055144</v>
       </c>
       <c r="F24">
-        <v>-2.96785831064952</v>
+        <v>0.3822334234262681</v>
       </c>
       <c r="G24">
-        <v>-12.34280621625883</v>
+        <v>-8.062778946405921</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-16.77541538355322</v>
       </c>
       <c r="E25">
-        <v>-37.44884676031288</v>
+        <v>-28.60182966498213</v>
       </c>
       <c r="F25">
-        <v>-3.053055069660047</v>
+        <v>0.4772297688119126</v>
       </c>
       <c r="G25">
-        <v>-12.82002683081302</v>
+        <v>-8.413512901637556</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-16.44929203892097</v>
       </c>
       <c r="E26">
-        <v>-37.39681740544108</v>
+        <v>-30.22648494763422</v>
       </c>
       <c r="F26">
-        <v>-3.491790752511374</v>
+        <v>0.3591261147251759</v>
       </c>
       <c r="G26">
-        <v>-13.13301855686323</v>
+        <v>-8.069361938892412</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-16.14844277680479</v>
       </c>
       <c r="E27">
-        <v>-36.85025687169931</v>
+        <v>-29.56228885632801</v>
       </c>
       <c r="F27">
-        <v>-3.380699228489335</v>
+        <v>0.392401633295632</v>
       </c>
       <c r="G27">
-        <v>-13.03105331611271</v>
+        <v>-8.043600416639602</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-15.88436517093641</v>
       </c>
       <c r="E28">
-        <v>-37.78033532220406</v>
+        <v>-28.89658514931088</v>
       </c>
       <c r="F28">
-        <v>-3.756630579962613</v>
+        <v>0.1023189659788844</v>
       </c>
       <c r="G28">
-        <v>-12.39332281872458</v>
+        <v>-8.057480440258256</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-15.68362849360673</v>
       </c>
       <c r="E29">
-        <v>-36.83471347831614</v>
+        <v>-29.20540548379115</v>
       </c>
       <c r="F29">
-        <v>-3.046008976531834</v>
+        <v>0.2124056803413275</v>
       </c>
       <c r="G29">
-        <v>-12.79981183544403</v>
+        <v>-8.994179049125426</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-15.55421951525013</v>
       </c>
       <c r="E30">
-        <v>-36.16273426898719</v>
+        <v>-29.69660371057296</v>
       </c>
       <c r="F30">
-        <v>-3.186629313361467</v>
+        <v>0.5519393965029973</v>
       </c>
       <c r="G30">
-        <v>-13.29271127664015</v>
+        <v>-8.434216106245085</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-15.51009018054704</v>
       </c>
       <c r="E31">
-        <v>-36.23529502404327</v>
+        <v>-29.32647782372689</v>
       </c>
       <c r="F31">
-        <v>-3.482180862271497</v>
+        <v>0.2403564532465884</v>
       </c>
       <c r="G31">
-        <v>-13.1785329726924</v>
+        <v>-8.835447083358035</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-15.54591806969532</v>
       </c>
       <c r="E32">
-        <v>-35.59242151967872</v>
+        <v>-28.18577756730611</v>
       </c>
       <c r="F32">
-        <v>-3.25062980726916</v>
+        <v>0.4925396551504531</v>
       </c>
       <c r="G32">
-        <v>-13.91860074193529</v>
+        <v>-8.998514190518971</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-15.65941628831595</v>
       </c>
       <c r="E33">
-        <v>-35.27958502984734</v>
+        <v>-28.25237846411106</v>
       </c>
       <c r="F33">
-        <v>-2.442490308078615</v>
+        <v>0.5115937621496474</v>
       </c>
       <c r="G33">
-        <v>-12.79202528970104</v>
+        <v>-9.199243899151307</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-15.83056350344995</v>
       </c>
       <c r="E34">
-        <v>-35.73441566166328</v>
+        <v>-27.43637834567103</v>
       </c>
       <c r="F34">
-        <v>-2.322077165672873</v>
+        <v>0.7823439910198601</v>
       </c>
       <c r="G34">
-        <v>-13.49280004747537</v>
+        <v>-9.240043310248929</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-16.04838273420216</v>
       </c>
       <c r="E35">
-        <v>-36.20556218416883</v>
+        <v>-27.203291819699</v>
       </c>
       <c r="F35">
-        <v>-3.434934099085424</v>
+        <v>0.5559793443264505</v>
       </c>
       <c r="G35">
-        <v>-14.13316478615593</v>
+        <v>-9.470959753216013</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-16.28685383855978</v>
       </c>
       <c r="E36">
-        <v>-34.5510515419082</v>
+        <v>-26.758254460187</v>
       </c>
       <c r="F36">
-        <v>-3.143217062882953</v>
+        <v>0.945403144056526</v>
       </c>
       <c r="G36">
-        <v>-12.79483053476419</v>
+        <v>-9.519032698744477</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-16.5380695823077</v>
       </c>
       <c r="E37">
-        <v>-35.78585110731563</v>
+        <v>-26.33826096496372</v>
       </c>
       <c r="F37">
-        <v>-3.051389222813017</v>
+        <v>1.011324621971311</v>
       </c>
       <c r="G37">
-        <v>-14.13354073337705</v>
+        <v>-10.03366658866162</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-16.78582787365172</v>
       </c>
       <c r="E38">
-        <v>-34.19100549894749</v>
+        <v>-25.86926372931878</v>
       </c>
       <c r="F38">
-        <v>-2.834942619033326</v>
+        <v>0.9648117923041184</v>
       </c>
       <c r="G38">
-        <v>-14.70227969420042</v>
+        <v>-9.620821714235097</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-17.02899177040317</v>
       </c>
       <c r="E39">
-        <v>-33.74675101977022</v>
+        <v>-24.77325202675315</v>
       </c>
       <c r="F39">
-        <v>-2.607134956324239</v>
+        <v>0.5797568022564075</v>
       </c>
       <c r="G39">
-        <v>-13.73655091085237</v>
+        <v>-9.897282596594152</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-17.26630801861606</v>
       </c>
       <c r="E40">
-        <v>-32.48571354181819</v>
+        <v>-24.4226171606545</v>
       </c>
       <c r="F40">
-        <v>-3.245140216490807</v>
+        <v>1.050935494438378</v>
       </c>
       <c r="G40">
-        <v>-13.14688813750352</v>
+        <v>-9.951005193417787</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-17.49914102610328</v>
       </c>
       <c r="E41">
-        <v>-33.63593503520114</v>
+        <v>-23.96569331033084</v>
       </c>
       <c r="F41">
-        <v>-3.519239534770539</v>
+        <v>0.7384322349974584</v>
       </c>
       <c r="G41">
-        <v>-15.15647484683329</v>
+        <v>-10.37615189635763</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-17.73478111228365</v>
       </c>
       <c r="E42">
-        <v>-32.97619118643514</v>
+        <v>-22.84853345569918</v>
       </c>
       <c r="F42">
-        <v>-2.901949258245778</v>
+        <v>0.8357736885004282</v>
       </c>
       <c r="G42">
-        <v>-13.51169270070896</v>
+        <v>-10.68375374019948</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-17.97247878738441</v>
       </c>
       <c r="E43">
-        <v>-31.98191447187685</v>
+        <v>-22.86815322599767</v>
       </c>
       <c r="F43">
-        <v>-3.121775601028891</v>
+        <v>0.880730844185163</v>
       </c>
       <c r="G43">
-        <v>-14.80952516588647</v>
+        <v>-10.54628628912671</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-18.21812353023489</v>
       </c>
       <c r="E44">
-        <v>-30.93078029428166</v>
+        <v>-22.29537969897924</v>
       </c>
       <c r="F44">
-        <v>-2.62035570007292</v>
+        <v>0.375751448499362</v>
       </c>
       <c r="G44">
-        <v>-14.1946922039347</v>
+        <v>-10.57181023362173</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-18.46619528365626</v>
       </c>
       <c r="E45">
-        <v>-31.49810688464758</v>
+        <v>-22.19167401219828</v>
       </c>
       <c r="F45">
-        <v>-4.024499747005889</v>
+        <v>0.5810871603053035</v>
       </c>
       <c r="G45">
-        <v>-13.87299756079002</v>
+        <v>-10.60649528088696</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-18.71900198452339</v>
       </c>
       <c r="E46">
-        <v>-31.79259864005719</v>
+        <v>-21.66232646279225</v>
       </c>
       <c r="F46">
-        <v>-2.737644240635301</v>
+        <v>0.6070962400184023</v>
       </c>
       <c r="G46">
-        <v>-14.38697484844249</v>
+        <v>-10.22091702297003</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-18.96691105574777</v>
       </c>
       <c r="E47">
-        <v>-31.09239212995905</v>
+        <v>-21.97079792752124</v>
       </c>
       <c r="F47">
-        <v>-3.488736561897253</v>
+        <v>0.7557086655502449</v>
       </c>
       <c r="G47">
-        <v>-15.41370367916191</v>
+        <v>-10.23705795140459</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-19.2122565482679</v>
       </c>
       <c r="E48">
-        <v>-30.02563564796552</v>
+        <v>-20.43858274593152</v>
       </c>
       <c r="F48">
-        <v>-3.13549916379107</v>
+        <v>0.751477364856745</v>
       </c>
       <c r="G48">
-        <v>-13.57458945402577</v>
+        <v>-10.84898907074334</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-19.44388290398187</v>
       </c>
       <c r="E49">
-        <v>-28.64321641583405</v>
+        <v>-19.43123795193966</v>
       </c>
       <c r="F49">
-        <v>-3.341268111748676</v>
+        <v>0.4560931461620805</v>
       </c>
       <c r="G49">
-        <v>-14.18389416430585</v>
+        <v>-9.751296285920576</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-19.66776044129002</v>
       </c>
       <c r="E50">
-        <v>-29.74722097359431</v>
+        <v>-20.25313355385528</v>
       </c>
       <c r="F50">
-        <v>-3.54426699911132</v>
+        <v>0.4958224751677475</v>
       </c>
       <c r="G50">
-        <v>-13.45824814818428</v>
+        <v>-10.03349036340171</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-19.87273368807941</v>
       </c>
       <c r="E51">
-        <v>-29.11291346758722</v>
+        <v>-19.23804717395394</v>
       </c>
       <c r="F51">
-        <v>-3.880483103824778</v>
+        <v>0.3631668909160319</v>
       </c>
       <c r="G51">
-        <v>-14.41618777504475</v>
+        <v>-10.06996638145645</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-20.06572999776497</v>
       </c>
       <c r="E52">
-        <v>-29.65953214628754</v>
+        <v>-18.91732788902803</v>
       </c>
       <c r="F52">
-        <v>-3.380304925605603</v>
+        <v>0.6230754472184048</v>
       </c>
       <c r="G52">
-        <v>-14.05251235887497</v>
+        <v>-10.04021694684072</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-20.24065475106345</v>
       </c>
       <c r="E53">
-        <v>-28.5085256959642</v>
+        <v>-18.41832785477253</v>
       </c>
       <c r="F53">
-        <v>-3.908244180594798</v>
+        <v>0.1439883314419079</v>
       </c>
       <c r="G53">
-        <v>-14.016954017544</v>
+        <v>-10.55259906954802</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-20.39915738737882</v>
       </c>
       <c r="E54">
-        <v>-28.35641017798103</v>
+        <v>-18.25113617968023</v>
       </c>
       <c r="F54">
-        <v>-3.884855226976754</v>
+        <v>0.3582099403776797</v>
       </c>
       <c r="G54">
-        <v>-12.82189742931256</v>
+        <v>-10.11348227230113</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-20.54233416495559</v>
       </c>
       <c r="E55">
-        <v>-28.07559494746407</v>
+        <v>-18.34521056939892</v>
       </c>
       <c r="F55">
-        <v>-2.8475106092686</v>
+        <v>0.03550285126907626</v>
       </c>
       <c r="G55">
-        <v>-13.93949453089797</v>
+        <v>-11.25347956247829</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-20.6662711508579</v>
       </c>
       <c r="E56">
-        <v>-25.82489081952431</v>
+        <v>-17.35363551880743</v>
       </c>
       <c r="F56">
-        <v>-3.371133241721807</v>
+        <v>0.5604525283015678</v>
       </c>
       <c r="G56">
-        <v>-14.33943971629979</v>
+        <v>-10.55754904129277</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-20.77758697030197</v>
       </c>
       <c r="E57">
-        <v>-27.06717031852775</v>
+        <v>-17.06141141678117</v>
       </c>
       <c r="F57">
-        <v>-3.608087737292605</v>
+        <v>0.2451676111220479</v>
       </c>
       <c r="G57">
-        <v>-13.86784264559486</v>
+        <v>-10.01808305419726</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-20.87113440075492</v>
       </c>
       <c r="E58">
-        <v>-27.12208407866463</v>
+        <v>-17.07903349243242</v>
       </c>
       <c r="F58">
-        <v>-3.475051104035602</v>
+        <v>0.1506591741366523</v>
       </c>
       <c r="G58">
-        <v>-14.105265064083</v>
+        <v>-10.62463734505061</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-20.9542821312621</v>
       </c>
       <c r="E59">
-        <v>-26.90267823079659</v>
+        <v>-16.31866356308281</v>
       </c>
       <c r="F59">
-        <v>-3.296305157492122</v>
+        <v>0.1783871162105602</v>
       </c>
       <c r="G59">
-        <v>-14.68932779028391</v>
+        <v>-10.59095351833607</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-21.02307895584389</v>
       </c>
       <c r="E60">
-        <v>-24.70011397532292</v>
+        <v>-15.83251356466633</v>
       </c>
       <c r="F60">
-        <v>-3.902907009418561</v>
+        <v>0.4591862700441338</v>
       </c>
       <c r="G60">
-        <v>-14.61278598036165</v>
+        <v>-10.32644462471513</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-21.0858076499435</v>
       </c>
       <c r="E61">
-        <v>-26.51479736553688</v>
+        <v>-16.43796040517718</v>
       </c>
       <c r="F61">
-        <v>-3.465219211331775</v>
+        <v>0.3793714140495958</v>
       </c>
       <c r="G61">
-        <v>-15.52222580495301</v>
+        <v>-10.44679864499316</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-21.1382316499279</v>
       </c>
       <c r="E62">
-        <v>-25.71377580373985</v>
+        <v>-15.38884261168019</v>
       </c>
       <c r="F62">
-        <v>-3.473977539881574</v>
+        <v>0.3047106600352764</v>
       </c>
       <c r="G62">
-        <v>-13.93395192013103</v>
+        <v>-10.52469282061361</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-21.1889490703589</v>
       </c>
       <c r="E63">
-        <v>-26.10973466502635</v>
+        <v>-15.38734745560326</v>
       </c>
       <c r="F63">
-        <v>-3.671673219131495</v>
+        <v>0.4964843407225843</v>
       </c>
       <c r="G63">
-        <v>-14.34051273232674</v>
+        <v>-11.05978058902983</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-21.23091439185966</v>
       </c>
       <c r="E64">
-        <v>-27.41663813224412</v>
+        <v>-15.95961013762873</v>
       </c>
       <c r="F64">
-        <v>-3.642267004699515</v>
+        <v>0.6000667142382458</v>
       </c>
       <c r="G64">
-        <v>-15.37968045565052</v>
+        <v>-11.23938676317546</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-21.27030391315613</v>
       </c>
       <c r="E65">
-        <v>-26.97497318032788</v>
+        <v>-15.75676314331278</v>
       </c>
       <c r="F65">
-        <v>-3.117439926042638</v>
+        <v>0.373425392832301</v>
       </c>
       <c r="G65">
-        <v>-15.1793554124298</v>
+        <v>-11.05520917525079</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-21.29794170175284</v>
       </c>
       <c r="E66">
-        <v>-25.31748468554736</v>
+        <v>-15.36991642767295</v>
       </c>
       <c r="F66">
-        <v>-3.600809701291609</v>
+        <v>0.02205761995423748</v>
       </c>
       <c r="G66">
-        <v>-15.44908840597756</v>
+        <v>-11.4405576876437</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-21.31538186496306</v>
       </c>
       <c r="E67">
-        <v>-24.56263852725977</v>
+        <v>-15.19536941532438</v>
       </c>
       <c r="F67">
-        <v>-3.188509707365822</v>
+        <v>0.08987523085403021</v>
       </c>
       <c r="G67">
-        <v>-14.62574310576735</v>
+        <v>-11.36606009073628</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-21.31802358643493</v>
       </c>
       <c r="E68">
-        <v>-26.40877418683666</v>
+        <v>-15.07345605009536</v>
       </c>
       <c r="F68">
-        <v>-3.956532201606189</v>
+        <v>0.3350984898395735</v>
       </c>
       <c r="G68">
-        <v>-15.06898618484049</v>
+        <v>-11.14242109831692</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-21.29995313508826</v>
       </c>
       <c r="E69">
-        <v>-25.90598227064159</v>
+        <v>-14.81282542661707</v>
       </c>
       <c r="F69">
-        <v>-4.155092696424633</v>
+        <v>0.1094586646236133</v>
       </c>
       <c r="G69">
-        <v>-15.73042354848822</v>
+        <v>-11.27946038727676</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-21.26260764081911</v>
       </c>
       <c r="E70">
-        <v>-23.89767616846412</v>
+        <v>-15.4184674680602</v>
       </c>
       <c r="F70">
-        <v>-3.709454228005778</v>
+        <v>0.2038975187471738</v>
       </c>
       <c r="G70">
-        <v>-14.89314862051212</v>
+        <v>-11.53966938455613</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-21.19562062127345</v>
       </c>
       <c r="E71">
-        <v>-24.98842159906987</v>
+        <v>-15.58849993969868</v>
       </c>
       <c r="F71">
-        <v>-3.7982005413373</v>
+        <v>0.004798585116909784</v>
       </c>
       <c r="G71">
-        <v>-15.49090339672112</v>
+        <v>-10.91139761482161</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-21.10696250246089</v>
       </c>
       <c r="E72">
-        <v>-25.91952589277185</v>
+        <v>-15.5806586767174</v>
       </c>
       <c r="F72">
-        <v>-3.849911376457059</v>
+        <v>0.269791660537666</v>
       </c>
       <c r="G72">
-        <v>-15.16785377713365</v>
+        <v>-11.0899307729403</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-20.99020602890402</v>
       </c>
       <c r="E73">
-        <v>-26.25071542344766</v>
+        <v>-14.7606735520112</v>
       </c>
       <c r="F73">
-        <v>-3.843306803154539</v>
+        <v>0.01836558643996009</v>
       </c>
       <c r="G73">
-        <v>-14.44662253011565</v>
+        <v>-11.82016778342534</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-20.85543291389495</v>
       </c>
       <c r="E74">
-        <v>-26.15776240078667</v>
+        <v>-15.56371772772343</v>
       </c>
       <c r="F74">
-        <v>-4.063855482312893</v>
+        <v>-0.09184703976770854</v>
       </c>
       <c r="G74">
-        <v>-14.50050046624246</v>
+        <v>-11.15585860072738</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-20.70107800687636</v>
       </c>
       <c r="E75">
-        <v>-26.09717535398007</v>
+        <v>-15.54625762731385</v>
       </c>
       <c r="F75">
-        <v>-4.266817093142412</v>
+        <v>-0.1956663263605706</v>
       </c>
       <c r="G75">
-        <v>-14.41719813320151</v>
+        <v>-11.2130822060477</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-20.53855630475244</v>
       </c>
       <c r="E76">
-        <v>-25.74438497120383</v>
+        <v>-15.31295513435293</v>
       </c>
       <c r="F76">
-        <v>-3.938440657529048</v>
+        <v>-0.1258192153239191</v>
       </c>
       <c r="G76">
-        <v>-15.18544366881628</v>
+        <v>-11.13407976934832</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-20.3678824256036</v>
       </c>
       <c r="E77">
-        <v>-25.38106204450783</v>
+        <v>-15.89810938433067</v>
       </c>
       <c r="F77">
-        <v>-3.755837003990731</v>
+        <v>-0.4419623211327392</v>
       </c>
       <c r="G77">
-        <v>-15.74118503769279</v>
+        <v>-11.26982412899096</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-20.20006374784189</v>
       </c>
       <c r="E78">
-        <v>-25.78235362913541</v>
+        <v>-15.80634418010858</v>
       </c>
       <c r="F78">
-        <v>-4.598627940007781</v>
+        <v>0.1093932235987922</v>
       </c>
       <c r="G78">
-        <v>-14.67639546695183</v>
+        <v>-10.85844518765235</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-20.03256346946131</v>
       </c>
       <c r="E79">
-        <v>-26.4192195133186</v>
+        <v>-15.6647321335659</v>
       </c>
       <c r="F79">
-        <v>-3.823331551603431</v>
+        <v>-0.6513131297400498</v>
       </c>
       <c r="G79">
-        <v>-15.26152859843509</v>
+        <v>-10.99540876501904</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-19.87217383256698</v>
       </c>
       <c r="E80">
-        <v>-25.79134117844234</v>
+        <v>-15.8127027466469</v>
       </c>
       <c r="F80">
-        <v>-4.13658034170687</v>
+        <v>-0.3340682952855064</v>
       </c>
       <c r="G80">
-        <v>-15.01001729676101</v>
+        <v>-10.84460824131945</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-19.71492451114429</v>
       </c>
       <c r="E81">
-        <v>-27.41317020078789</v>
+        <v>-16.89344309117113</v>
       </c>
       <c r="F81">
-        <v>-4.132021835889264</v>
+        <v>-0.3629161900879991</v>
       </c>
       <c r="G81">
-        <v>-14.2032998288516</v>
+        <v>-10.3362075041136</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-19.55905562540109</v>
       </c>
       <c r="E82">
-        <v>-27.72157936734701</v>
+        <v>-17.10941008006222</v>
       </c>
       <c r="F82">
-        <v>-4.476249910122599</v>
+        <v>-0.1442031730942485</v>
       </c>
       <c r="G82">
-        <v>-14.3987218937302</v>
+        <v>-10.31985771611175</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-19.4035757262148</v>
       </c>
       <c r="E83">
-        <v>-27.98125059900926</v>
+        <v>-18.77581551955715</v>
       </c>
       <c r="F83">
-        <v>-4.269246694734822</v>
+        <v>-0.4917538289802119</v>
       </c>
       <c r="G83">
-        <v>-14.2701649139469</v>
+        <v>-10.60781892839466</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-19.23994541179069</v>
       </c>
       <c r="E84">
-        <v>-28.37169814886772</v>
+        <v>-18.26263642183868</v>
       </c>
       <c r="F84">
-        <v>-3.923735479394551</v>
+        <v>-0.6348882608773413</v>
       </c>
       <c r="G84">
-        <v>-15.07665655244918</v>
+        <v>-10.80299819402629</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-19.07440534499229</v>
       </c>
       <c r="E85">
-        <v>-29.55239798355793</v>
+        <v>-20.20121010587227</v>
       </c>
       <c r="F85">
-        <v>-3.993560224511327</v>
+        <v>-0.4769492467573791</v>
       </c>
       <c r="G85">
-        <v>-13.5608882664116</v>
+        <v>-10.58140471999407</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-18.90011134474134</v>
       </c>
       <c r="E86">
-        <v>-29.83915853608638</v>
+        <v>-19.51614205105313</v>
       </c>
       <c r="F86">
-        <v>-4.973605840600436</v>
+        <v>-0.6279531689811038</v>
       </c>
       <c r="G86">
-        <v>-15.01960525627188</v>
+        <v>-10.6256685891641</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-18.7289684769297</v>
       </c>
       <c r="E87">
-        <v>-30.87063764108682</v>
+        <v>-21.34537829374929</v>
       </c>
       <c r="F87">
-        <v>-4.012366649657085</v>
+        <v>-0.5469139859652281</v>
       </c>
       <c r="G87">
-        <v>-14.43178958472124</v>
+        <v>-9.837439109076653</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-18.5591729187846</v>
       </c>
       <c r="E88">
-        <v>-30.56403304484834</v>
+        <v>-21.48718554122424</v>
       </c>
       <c r="F88">
-        <v>-4.560923969301959</v>
+        <v>-0.4230432380202013</v>
       </c>
       <c r="G88">
-        <v>-14.83690534978577</v>
+        <v>-10.25015997313509</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-18.40290175118313</v>
       </c>
       <c r="E89">
-        <v>-32.19360780631469</v>
+        <v>-24.03963708475809</v>
       </c>
       <c r="F89">
-        <v>-4.337478489336014</v>
+        <v>-0.8332640297649613</v>
       </c>
       <c r="G89">
-        <v>-13.48424855356718</v>
+        <v>-10.03983055664123</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-18.2610654430079</v>
       </c>
       <c r="E90">
-        <v>-33.69611091408658</v>
+        <v>-24.71111583212239</v>
       </c>
       <c r="F90">
-        <v>-4.635518453924054</v>
+        <v>-0.7307908402016484</v>
       </c>
       <c r="G90">
-        <v>-14.2574427555544</v>
+        <v>-9.886488473082194</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-18.14598464671405</v>
       </c>
       <c r="E91">
-        <v>-34.68055490083334</v>
+        <v>-26.98060078167302</v>
       </c>
       <c r="F91">
-        <v>-4.690697663359335</v>
+        <v>-1.147344500740811</v>
       </c>
       <c r="G91">
-        <v>-14.95603362547827</v>
+        <v>-9.774028039075398</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-18.05782006584495</v>
       </c>
       <c r="E92">
-        <v>-36.56730273735006</v>
+        <v>-28.42762736917352</v>
       </c>
       <c r="F92">
-        <v>-4.787701142961962</v>
+        <v>-1.11389005481135</v>
       </c>
       <c r="G92">
-        <v>-13.8971508643747</v>
+        <v>-10.1318828001793</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-18.00762854180928</v>
       </c>
       <c r="E93">
-        <v>-37.16366442808786</v>
+        <v>-29.8350302440295</v>
       </c>
       <c r="F93">
-        <v>-4.67028503381955</v>
+        <v>-1.149456837617949</v>
       </c>
       <c r="G93">
-        <v>-14.82545984549833</v>
+        <v>-9.757045145510206</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-17.99072170227195</v>
       </c>
       <c r="E94">
-        <v>-37.62311343089701</v>
+        <v>-31.37699093599293</v>
       </c>
       <c r="F94">
-        <v>-4.481320346995135</v>
+        <v>-1.082658946991003</v>
       </c>
       <c r="G94">
-        <v>-15.12933485143637</v>
+        <v>-9.933810829540715</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-18.01195588114962</v>
       </c>
       <c r="E95">
-        <v>-38.77872371597393</v>
+        <v>-33.93335895780609</v>
       </c>
       <c r="F95">
-        <v>-4.870457531603842</v>
+        <v>-1.60271628614256</v>
       </c>
       <c r="G95">
-        <v>-14.81770071257354</v>
+        <v>-10.10712641459406</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-18.06141160873887</v>
       </c>
       <c r="E96">
-        <v>-41.26336993141863</v>
+        <v>-35.14799675883713</v>
       </c>
       <c r="F96">
-        <v>-4.501911075526522</v>
+        <v>-1.684681583914766</v>
       </c>
       <c r="G96">
-        <v>-15.07793320655423</v>
+        <v>-10.24928406832477</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-18.12912623546379</v>
       </c>
       <c r="E97">
-        <v>-43.37667752231042</v>
+        <v>-37.63340924177127</v>
       </c>
       <c r="F97">
-        <v>-5.57631519410112</v>
+        <v>-1.795406969544767</v>
       </c>
       <c r="G97">
-        <v>-15.19229817874025</v>
+        <v>-9.707857412041337</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-18.20089192959292</v>
       </c>
       <c r="E98">
-        <v>-44.35391568740859</v>
+        <v>-40.47981469984817</v>
       </c>
       <c r="F98">
-        <v>-4.522785105709667</v>
+        <v>-1.948983800921587</v>
       </c>
       <c r="G98">
-        <v>-15.53298207266839</v>
+        <v>-10.83587530066218</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-18.25692692063833</v>
       </c>
       <c r="E99">
-        <v>-46.81597362476038</v>
+        <v>-42.34851060334152</v>
       </c>
       <c r="F99">
-        <v>-4.832880301110648</v>
+        <v>-2.185453701561748</v>
       </c>
       <c r="G99">
-        <v>-15.6406504849782</v>
+        <v>-10.61463688789435</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-18.28232944543722</v>
       </c>
       <c r="E100">
-        <v>-47.52581247022363</v>
+        <v>-44.4343924632498</v>
       </c>
       <c r="F100">
-        <v>-4.589873753294996</v>
+        <v>-2.387006259439104</v>
       </c>
       <c r="G100">
-        <v>-15.09305594459826</v>
+        <v>-11.50001609033401</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-18.26194873344578</v>
       </c>
       <c r="E101">
-        <v>-48.7715297899012</v>
+        <v>-46.16129980871917</v>
       </c>
       <c r="F101">
-        <v>-4.903105147682976</v>
+        <v>-2.528579218781957</v>
       </c>
       <c r="G101">
-        <v>-16.10080205139569</v>
+        <v>-11.12263426506088</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-18.17945897116466</v>
       </c>
       <c r="E102">
-        <v>-51.34406730170475</v>
+        <v>-48.27415262297088</v>
       </c>
       <c r="F102">
-        <v>-5.575065187690296</v>
+        <v>-2.901107636964534</v>
       </c>
       <c r="G102">
-        <v>-15.61339431144698</v>
+        <v>-10.92797062148599</v>
       </c>
     </row>
   </sheetData>
